--- a/site/exports/dlut-physics.xlsx
+++ b/site/exports/dlut-physics.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,10 +569,118 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>赵纪军</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>物理学院</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/zhaojj/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>目录栏目、主页身份标签及旧文“至今”均不独立证实现时人事状态；不启用在岗导师快捷导航。；仅核原序前三，不代表院系全员、全职或完整履历。；论文仅核官网书目，未核出版社记录、DOI及全文。；院系行政父级和校区未核实，不推校级直属。；未取得大工离职时间、现时正式任职合同或兼聘关系；SCNU个人页首次403，后续来源检索停止，摘要不作事实。；来源差异/限制：大工主页工作经历列2005.12至今教授，页面更新日期未获得可读值。；河南师大讲座报道及专家简介列华南师范大学物理学院教授。；保留来源时点与差异；school_id大工只代表此批历史职业资料来源，不断言当前仍在大工，不静默移校、不建重复人物。；来源任职差异说明中的河南师范大学报道日期：2026-04-30；仅归于该原报道，不据此判定现任单位。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>张钰如</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>物理学院</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2014011021/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>目录栏目、主页身份标签及旧文“至今”均不独立证实现时人事状态；不启用在岗导师快捷导航。；仅核原序前三，不代表院系全员、全职或完整履历。；论文仅核官网书目，未核出版社记录、DOI及全文。；院系行政父级和校区未核实，不推校级直属。；简介Bogaerts教授、Julian Schulze博士为明确合作关系，不认定博士或博士后导师。；未证实大工或安特卫普明确授位事件；本人博士生导师资格与其自己的导师关系不同。；来源差异/限制：2013-12；2014-01；直接攻博，不补硕士；同页简历结束2013.12，教育表结束2014.01，保留冲突不选择。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -666,7 +774,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1144,8 +1252,963 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>赵纪军</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1988-09</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1992-07</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>核物理</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>学士标签及毕业年份不等授位证据。；Historical 39-school classification uses exact matches in frozen baseline institution registry; unknown historical/abbreviated institution is not asserted non-985. Geography is institution-location normalization, not nationality or study location.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/zhaojj/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>赵纪军</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1992-09</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1994-07</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>核物理</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>仅教育经历硕士标签，无明确授位动词。；Historical 39-school classification uses exact matches in frozen baseline institution registry; unknown historical/abbreviated institution is not asserted non-985. Geography is institution-location normalization, not nationality or study location.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/zhaojj/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>赵纪军</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1994-09</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1996-10</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>凝聚态物理</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>学习时间来自大工主页；1996获博士以河南师大2026讲座专家简介明确表述为据，结束月不作授位月。；Historical 39-school classification uses exact matches in frozen baseline institution registry; unknown historical/abbreviated institution is not asserted non-985. Geography is institution-location normalization, not nationality or study location.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/zhaojj/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>赵纪军</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>postdoc</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>意大利国际理论物理中心</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1997-02</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1998-08</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>博士后为非学位任职/训练，不记博士学位。；Historical 39-school classification uses exact matches in frozen baseline institution registry; unknown historical/abbreviated institution is not asserted non-985. Geography is institution-location normalization, not nationality or study location.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（event_kind）：postdoc</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/zhaojj/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>赵纪军</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>postdoc</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>美国北卡大学</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1998-08</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2001-07</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>保留来源简称，不推具体校区。；Historical 39-school classification uses exact matches in frozen baseline institution registry; unknown historical/abbreviated institution is not asserted non-985. Geography is institution-location normalization, not nationality or study location.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（event_kind）：postdoc</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/zhaojj/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>赵纪军</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2005-12</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>原页写“2005.12 - 至今”；与2026讲座列示华南师大身份并存，不能认定在大工当前在岗或已正式离职。；任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/zhaojj/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>赵纪军</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>助理教授</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>美国北卡大学</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2001-08</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2002-12</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>不扩写来源未明确的北卡校区。；任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/zhaojj/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>赵纪军</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>研究员</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>美国华盛顿州立大学</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2002-12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2005-10</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/zhaojj/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>张钰如</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2005-09</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2009-07</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>光信息科学与技术</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Historical 39-school classification uses exact matches in frozen baseline institution registry; unknown historical/abbreviated institution is not asserted non-985. Geography is institution-location normalization, not nationality or study location.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2014011021/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>张钰如</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>等离子体物理</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>直接攻博，不补硕士；同页简历结束2013.12，教育表结束2014.01，保留冲突不选择。；Historical 39-school classification uses exact matches in frozen baseline institution registry; unknown historical/abbreviated institution is not asserted non-985. Geography is institution-location normalization, not nationality or study location.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2014011021/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>张钰如</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>双博士学位（原文标签）</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>比利时安特卫普大学</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2013-04</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2013-10</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>仅保留原文双博士学位标签；未明确授位，不擅自确定联合学位结构或新增硕士；化学系为院系，不当专业。；Historical 39-school classification uses exact matches in frozen baseline institution registry; unknown historical/abbreviated institution is not asserted non-985. Geography is institution-location normalization, not nationality or study location.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2014011021/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>张钰如</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>postdoc</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>比利时安特卫普大学</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2015-03</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2016-08</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Historical 39-school classification uses exact matches in frozen baseline institution registry; unknown historical/abbreviated institution is not asserted non-985. Geography is institution-location normalization, not nationality or study location.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（event_kind）：postdoc</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2014011021/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>张钰如</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>讲师</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学物理学院</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2017-12</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2014011021/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>张钰如</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学物理学院</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2017-12</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2014011021/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>张钰如</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>教授（破格）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学物理学院</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2014011021/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S8"/>
+  <autoFilter ref="A1:S23"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1154,6 +2217,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1165,18 +2243,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="32.2" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1244,8 +2322,61 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>赵纪军</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>王广厚</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>博士导师（原文师从，紧接1996年博士授位句）</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；仅接受明确博士语境的师承关系；导师现职未核。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.htu.edu.cn/physics/2026/0430/c2197a382682/page.htm</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L2"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1256,18 +2387,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
     <col width="22.4" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="49" customWidth="1" min="8" max="8"/>
-    <col width="58.8" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1447,13 +2578,229 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>赵纪军</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2D tetragonal transition-metal phosphides: an ideal platform to screen metal shrouded crystals for multifunctional applications</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/zhaojj/zh_CN/lwcg/719270/list/index.htm</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/zhaojj/zh_CN/lwcg/719270/list/index.htm</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；URL为书目原链接，文章详情未另读；不据网站迁移/上传时间校正论文年份。</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>赵纪军</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2D Boron Sheets: Structure, Growth, and Electronic and Thermal Transport Properties</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/zhaojj/zh_CN/lwcg/719270/list/index.htm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/zhaojj/zh_CN/lwcg/719270/list/index.htm</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；URL为书目原链接，文章详情未另读；不据网站迁移/上传时间校正论文年份。</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>张钰如</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>面向半导体工艺的平面线圈感性耦合氩等离子体源的三维流体模拟研究</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2014011021/zh_CN/lwcg/825758/list/index.htm</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2014011021/zh_CN/lwcg/825758/list/index.htm</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；URL为书目原链接，文章详情未另读；不据网站迁移/上传时间校正论文年份。</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>张钰如</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Effects of external parameters on plasma characteristics and uniformity in a dual cylindrical inductively coupled plasma</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2014011021/zh_CN/lwcg/825758/list/index.htm</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2014011021/zh_CN/lwcg/825758/list/index.htm</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；URL为书目原链接，文章详情未另读；不据网站迁移/上传时间校正论文年份。</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1465,14 +2812,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="43.4" customWidth="1" min="2" max="2"/>
+    <col width="62.99999999999999" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="25.2" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="44.8" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1625,12 +2972,278 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>赵纪军</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-dlut-zhaojijun-s001-f92caa9bb511</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/zhaojj/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T10:34:15.767448+00:00</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>赵纪军</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-dlut-zhaojijun-s002-b971f6401c44</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/zhaojj/zh_CN/lwcg/719270/list/index.htm</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T10:35:08.181689+00:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>赵纪军</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-dlut-zhaojijun-s003-abdc7e69cdeb</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>https://physics.dlut.edu.cn/szdw/jslb.htm</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T10:32:51.772019+00:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>赵纪军</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-dlut-zhaojijun-s004-9202d9959fa7</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.htu.edu.cn/physics/2026/0430/c2197a382682/page.htm</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T10:35:34.687899+00:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>张钰如</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-dlut-zhangyuru-s001-f03754b983e7</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2014011021/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T10:34:43.820064+00:00</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>张钰如</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-dlut-zhangyuru-s002-cfd39931e2f5</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/2014011021/zh_CN/lwcg/825758/list/index.htm</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T10:35:19.020292+00:00</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>张钰如</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-dlut-zhangyuru-s003-abdc7e69cdeb</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>https://physics.dlut.edu.cn/szdw/jslb.htm</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T10:32:51.772019+00:00</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
